--- a/artfynd/A 34130-2022 artfynd.xlsx
+++ b/artfynd/A 34130-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34130-2022 artfynd.xlsx
+++ b/artfynd/A 34130-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74253872</v>
       </c>
       <c r="B2" t="n">
-        <v>96974</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520592.2733924483</v>
+        <v>520592</v>
       </c>
       <c r="R2" t="n">
-        <v>6273722.905593473</v>
+        <v>6273723</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1991-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1991-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74269585</v>
       </c>
       <c r="B3" t="n">
-        <v>97050</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520592.2733924483</v>
+        <v>520592</v>
       </c>
       <c r="R3" t="n">
-        <v>6273722.905593473</v>
+        <v>6273723</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1991-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1991-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,12 +900,7 @@
         <v>74702057</v>
       </c>
       <c r="B4" t="n">
-        <v>104541</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107042</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520292.2985905486</v>
+        <v>520292</v>
       </c>
       <c r="R4" t="n">
-        <v>6273719.798915553</v>
+        <v>6273720</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1000,19 +965,9 @@
           <t>1982-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1982-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 34130-2022 artfynd.xlsx
+++ b/artfynd/A 34130-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74253872</v>
       </c>
       <c r="B2" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74269585</v>
       </c>
       <c r="B3" t="n">
-        <v>99339</v>
+        <v>99344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74702057</v>
       </c>
       <c r="B4" t="n">
-        <v>107042</v>
+        <v>107051</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34130-2022 artfynd.xlsx
+++ b/artfynd/A 34130-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74253872</v>
       </c>
       <c r="B2" t="n">
-        <v>99268</v>
+        <v>99269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74269585</v>
       </c>
       <c r="B3" t="n">
-        <v>99344</v>
+        <v>99345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74702057</v>
       </c>
       <c r="B4" t="n">
-        <v>107051</v>
+        <v>107056</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34130-2022 artfynd.xlsx
+++ b/artfynd/A 34130-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74253872</v>
       </c>
       <c r="B2" t="n">
-        <v>99269</v>
+        <v>99296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74269585</v>
       </c>
       <c r="B3" t="n">
-        <v>99345</v>
+        <v>99372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74702057</v>
       </c>
       <c r="B4" t="n">
-        <v>107056</v>
+        <v>107084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34130-2022 artfynd.xlsx
+++ b/artfynd/A 34130-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74253872</v>
       </c>
       <c r="B2" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74269585</v>
       </c>
       <c r="B3" t="n">
-        <v>99372</v>
+        <v>99378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74702057</v>
       </c>
       <c r="B4" t="n">
-        <v>107084</v>
+        <v>107090</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34130-2022 artfynd.xlsx
+++ b/artfynd/A 34130-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74253872</v>
       </c>
       <c r="B2" t="n">
-        <v>99302</v>
+        <v>99309</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74269585</v>
       </c>
       <c r="B3" t="n">
-        <v>99378</v>
+        <v>99385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74702057</v>
       </c>
       <c r="B4" t="n">
-        <v>107090</v>
+        <v>107097</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34130-2022 artfynd.xlsx
+++ b/artfynd/A 34130-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74253872</v>
       </c>
       <c r="B2" t="n">
-        <v>99309</v>
+        <v>99313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74269585</v>
       </c>
       <c r="B3" t="n">
-        <v>99385</v>
+        <v>99389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74702057</v>
       </c>
       <c r="B4" t="n">
-        <v>107097</v>
+        <v>107101</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34130-2022 artfynd.xlsx
+++ b/artfynd/A 34130-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74253872</v>
       </c>
       <c r="B2" t="n">
-        <v>99313</v>
+        <v>99320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74269585</v>
       </c>
       <c r="B3" t="n">
-        <v>99389</v>
+        <v>99396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74702057</v>
       </c>
       <c r="B4" t="n">
-        <v>107101</v>
+        <v>107109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34130-2022 artfynd.xlsx
+++ b/artfynd/A 34130-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74253872</v>
       </c>
       <c r="B2" t="n">
-        <v>99323</v>
+        <v>99328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74269585</v>
       </c>
       <c r="B3" t="n">
-        <v>99399</v>
+        <v>99404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74702057</v>
       </c>
       <c r="B4" t="n">
-        <v>107112</v>
+        <v>107117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34130-2022 artfynd.xlsx
+++ b/artfynd/A 34130-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74253872</v>
       </c>
       <c r="B2" t="n">
-        <v>99328</v>
+        <v>99336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74269585</v>
       </c>
       <c r="B3" t="n">
-        <v>99404</v>
+        <v>99412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74702057</v>
       </c>
       <c r="B4" t="n">
-        <v>107117</v>
+        <v>107125</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34130-2022 artfynd.xlsx
+++ b/artfynd/A 34130-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74253872</v>
       </c>
       <c r="B2" t="n">
-        <v>99336</v>
+        <v>99346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74269585</v>
       </c>
       <c r="B3" t="n">
-        <v>99412</v>
+        <v>99422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74702057</v>
       </c>
       <c r="B4" t="n">
-        <v>107125</v>
+        <v>107135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34130-2022 artfynd.xlsx
+++ b/artfynd/A 34130-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74253872</v>
+        <v>74702057</v>
       </c>
       <c r="B2" t="n">
-        <v>99346</v>
+        <v>107663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222322</v>
+        <v>1174</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Pedicularis sylvatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Äskebäck 350 m S den östra gården, Sm</t>
+          <t>Äskebäck 450 m SSV den östra gården, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520592</v>
+        <v>520292</v>
       </c>
       <c r="R2" t="n">
-        <v>6273723</v>
+        <v>6273720</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -740,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1991-01-01</t>
+          <t>1982-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1991-12-31</t>
+          <t>1982-12-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4F5e 0611. SOM: Carex hostiana. LEG: Ivar Björegren</t>
+          <t>Smålands flora 2007: KOO: 4F5e 0608. SOM: Pedicularis sylvatica. LEG: Thomas Karlsson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Fuktig betad hagmark</t>
+          <t>Fuktig ogödslad betesmark, rikligt</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74269585</v>
+        <v>74253872</v>
       </c>
       <c r="B3" t="n">
-        <v>99422</v>
+        <v>99802</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222361</v>
+        <v>222322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4F5e 0611. SOM: Carex pulicaris. LEG: Ivar Björegren</t>
+          <t>Smålands flora 2007: KOO: 4F5e 0611. SOM: Carex hostiana. LEG: Ivar Björegren</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74702057</v>
+        <v>74269585</v>
       </c>
       <c r="B4" t="n">
-        <v>107135</v>
+        <v>99878</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,16 +908,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1174</v>
+        <v>222361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -928,14 +928,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Äskebäck 450 m SSV den östra gården, Sm</t>
+          <t>Äskebäck 350 m S den östra gården, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520292</v>
+        <v>520592</v>
       </c>
       <c r="R4" t="n">
-        <v>6273720</v>
+        <v>6273723</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -962,17 +962,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1982-01-01</t>
+          <t>1991-01-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1982-12-31</t>
+          <t>1991-12-31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4F5e 0608. SOM: Pedicularis sylvatica. LEG: Thomas Karlsson</t>
+          <t>Smålands flora 2007: KOO: 4F5e 0611. SOM: Carex pulicaris. LEG: Ivar Björegren</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +986,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Fuktig ogödslad betesmark, rikligt</t>
+          <t>Fuktig betad hagmark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 34130-2022 artfynd.xlsx
+++ b/artfynd/A 34130-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74702057</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74253872</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,8 +1020,18 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74269585</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>